--- a/Data/True_data/prior_data/balance_sheet.xlsx
+++ b/Data/True_data/prior_data/balance_sheet.xlsx
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>265.53</v>
+        <v>469.12</v>
       </c>
     </row>
     <row r="7">
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>256.57</v>
+        <v>183.5</v>
       </c>
     </row>
     <row r="8">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>102.5</v>
+        <v>81.73</v>
       </c>
     </row>
     <row r="9">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>49.99</v>
+        <v>49.58</v>
       </c>
     </row>
     <row r="10">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>674.6</v>
+        <v>783.92</v>
       </c>
     </row>
     <row r="11">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>346.8</v>
+        <v>254.25</v>
       </c>
     </row>
     <row r="12">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>85.2</v>
+        <v>65.23</v>
       </c>
     </row>
     <row r="13">
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>1106.6</v>
+        <v>1103.41</v>
       </c>
     </row>
     <row r="14">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>188.09</v>
+        <v>67.02</v>
       </c>
     </row>
     <row r="15">
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>57.01</v>
+        <v>160.33</v>
       </c>
     </row>
     <row r="16">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>53.47</v>
+        <v>27.59</v>
       </c>
     </row>
     <row r="17">
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>69.04000000000001</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="18">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>367.61</v>
+        <v>328.43</v>
       </c>
     </row>
     <row r="19">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>199.04</v>
+        <v>294.82</v>
       </c>
     </row>
     <row r="20">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>566.65</v>
+        <v>623.26</v>
       </c>
     </row>
     <row r="21">
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>102.46</v>
+        <v>131.34</v>
       </c>
     </row>
     <row r="22">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>181.61</v>
+        <v>164.32</v>
       </c>
     </row>
     <row r="23">
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>255.89</v>
+        <v>184.48</v>
       </c>
     </row>
     <row r="24">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>539.95</v>
+        <v>480.15</v>
       </c>
     </row>
     <row r="25">
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1106.6</v>
+        <v>1103.41</v>
       </c>
     </row>
   </sheetData>
